--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -618,42 +618,64 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ISO pre-audit / dry run</t>
+          <t>Release v1.4.1 — defect corrections</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>f1b8445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ISO pre-audit / dry run</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>ISO 9001 surveillance audit</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -776,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Actual timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Commits by month" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Open actions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actual timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commits by month" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open actions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -464,17 +464,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Project start — first commit</t>
+          <t>Decision to move from the 2025 PC appliance to a portable AI supercomputer (DGX Spark)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4b90b36</t>
+          <t>EM26-18 CR-2026-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -486,17 +486,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Phase 0b auth + vertical packs (single-day batch)</t>
+          <t>First DGX Spark; 2025 code ported — first commit</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>c9bad3d…b9f076e</t>
+          <t>4b90b36, c751d79</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -508,17 +508,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>TRT-LLM platform, evaluation harness, security enablement</t>
+          <t>Client requirements: personal assistant, conversation assistance, DoD FMR knowledge base</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80375c6, 12f7219, 9810e98</t>
+          <t>EM26-18 CR-2026-02; 95d3512</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -530,17 +530,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>RAG overhaul, Silent Assistant v2</t>
+          <t>TensorRT-LLM integrated beside Ollama</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7e582e1, 7f2658a</t>
+          <t>06e788a</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -552,17 +552,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Voice redesign</t>
+          <t>Own dual-loop conversation architecture; Nemotron speech recognition</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ff29843</t>
+          <t>ddc0aa3, d89aeda</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -574,17 +574,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Release v1.4.0 + QMS documentation</t>
+          <t>Field-deployment hotspot (Project Lead design review)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>eaa7b1a, 9efb134</t>
+          <t>EM26-18 CR-2026-05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Deployment of v1.4.0 code; login restored</t>
+          <t>Silent Assistant (law-firm request) and Boardroom</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>REG-08</t>
+          <t>ec9b180, f540976, e1a337b</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -618,17 +618,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Release v1.4.1 — defect corrections</t>
+          <t>Document Studio (Gulf client request)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>f1b8445</t>
+          <t>2d23f40, 66356f9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -640,42 +640,196 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ISO pre-audit / dry run</t>
+          <t>Phase 0b auth + vertical packs (single-day batch)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>c9bad3d…b9f076e</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>TRT-LLM platform, evaluation harness, security enablement</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>80375c6, 12f7219, 9810e98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>RAG overhaul, Silent Assistant v2</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7e582e1, 7f2658a</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Voice redesign</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ff29843</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Release v1.4.0 + QMS documentation</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>eaa7b1a, 9efb134</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Deployment of v1.4.0 code; login restored</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>REG-08</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Release v1.4.1 — defect corrections</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>f1b8445</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ISO pre-audit / dry run</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>ISO 9001 surveillance audit</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Scheduled</t>
         </is>
@@ -798,7 +952,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -851,11 +1005,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D14</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+          <t>D14 / REG-03 R-02</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -868,8 +1030,16 @@
           <t>NC-2026-008</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -882,8 +1052,16 @@
           <t>REG-09 A-1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-10-07</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Anita Johan</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -896,8 +1074,16 @@
           <t>NC-2026-010 / LL-2026-12</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Unit suites done 2026-10-07; API tests open</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -910,8 +1096,16 @@
           <t>EM26-15</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-10-06</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -924,8 +1118,16 @@
           <t>NC-2026-011</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>From v1.4.1 (2026-10-06)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -935,11 +1137,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>C1–C3</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+          <t>C1–C3 / R-10</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -949,11 +1159,41 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>B3/D10</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+          <t>B3/D10 / R-06</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Hotspot configuration under version control</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>EM26-18 AC-26</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
+++ b/docs/qms/evidence-2026/12_Scheduling_Review/EM26-12_SDLC_Record.xlsx
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
